--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>An organization acting as a manufacturer or deployer (owner) of an AI system, containing required regulatory contacts.</t>
+    <t>An Organization profile representing an organization involved in manufacturing, providing, deploying, or operating an AI system, including relevant accountability and contact information.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -4561,7 +4561,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>260</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -6665,7 +6665,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>350</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$54</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,7 +595,7 @@
 </t>
   </si>
   <si>
-    <t>Name used for the organization</t>
+    <t>Name of the legal entity</t>
   </si>
   <si>
     <t>A name associated with the organization.</t>
@@ -687,13 +687,16 @@
     <t>.contactParty</t>
   </si>
   <si>
-    <t>Organization.contact:dpo</t>
-  </si>
-  <si>
-    <t>dpo</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.id</t>
+    <t>Organization.contact:officialContact</t>
+  </si>
+  <si>
+    <t>officialContact</t>
+  </si>
+  <si>
+    <t>Official contact details of the legal entity</t>
+  </si>
+  <si>
+    <t>Organization.contact:officialContact.id</t>
   </si>
   <si>
     <t>Organization.contact.id</t>
@@ -712,7 +715,7 @@
 </t>
   </si>
   <si>
-    <t>Organization.contact:dpo.extension</t>
+    <t>Organization.contact:officialContact.extension</t>
   </si>
   <si>
     <t>Organization.contact.extension</t>
@@ -731,7 +734,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Organization.contact:dpo.purpose</t>
+    <t>Organization.contact:officialContact.purpose</t>
   </si>
   <si>
     <t>Organization.contact.purpose</t>
@@ -766,7 +769,7 @@
     <t>ExtendedContactDetail.purpose</t>
   </si>
   <si>
-    <t>Organization.contact:dpo.name</t>
+    <t>Organization.contact:officialContact.name</t>
   </si>
   <si>
     <t>Organization.contact.name</t>
@@ -788,288 +791,79 @@
     <t>ExtendedContactDetail.name</t>
   </si>
   <si>
-    <t>Organization.contact:dpo.name.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.id</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.use</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|5.0.0</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./NamePurpose</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.text</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.text</t>
-  </si>
-  <si>
-    <t>Data Protection Officer</t>
-  </si>
-  <si>
-    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
-    <t>HumanName.text</t>
-  </si>
-  <si>
-    <t>implied by XPN.11</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.family</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surname
+    <t>Organization.contact:officialContact.telecom</t>
+  </si>
+  <si>
+    <t>Organization.contact.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
 </t>
   </si>
   <si>
-    <t>Family name (often called 'Surname')</t>
-  </si>
-  <si>
-    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
-  </si>
-  <si>
-    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
-  </si>
-  <si>
-    <t>HumanName.family</t>
-  </si>
-  <si>
-    <t>XPN.1/FN.1</t>
-  </si>
-  <si>
-    <t>./part[partType = FAM]</t>
-  </si>
-  <si>
-    <t>./FamilyName</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.given</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.given</t>
-  </si>
-  <si>
-    <t>first name
-middle name</t>
-  </si>
-  <si>
-    <t>Given names (not always 'first'). Includes middle names</t>
-  </si>
-  <si>
-    <t>Given name.</t>
-  </si>
-  <si>
-    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
-  </si>
-  <si>
-    <t>HumanName.given</t>
-  </si>
-  <si>
-    <t>XPN.2 + XPN.3</t>
-  </si>
-  <si>
-    <t>./part[partType = GIV]</t>
-  </si>
-  <si>
-    <t>./GivenNames</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.prefix</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.prefix</t>
-  </si>
-  <si>
-    <t>Parts that come before the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.prefix</t>
-  </si>
-  <si>
-    <t>XPN.5</t>
-  </si>
-  <si>
-    <t>./part[partType = PFX]</t>
-  </si>
-  <si>
-    <t>./TitleCode</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.suffix</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.suffix</t>
-  </si>
-  <si>
-    <t>Parts that come after the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.suffix</t>
-  </si>
-  <si>
-    <t>XPN/4</t>
-  </si>
-  <si>
-    <t>./part[partType = SFX]</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.name.period</t>
-  </si>
-  <si>
-    <t>Organization.contact.name.period</t>
+    <t>Contact details (e.g.phone/fax/url)</t>
+  </si>
+  <si>
+    <t>The contact details application for the purpose defined.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.telecom</t>
+  </si>
+  <si>
+    <t>Organization.contact:officialContact.address</t>
+  </si>
+  <si>
+    <t>Organization.contact.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Address for the contact</t>
+  </si>
+  <si>
+    <t>Address for the contact.</t>
+  </si>
+  <si>
+    <t>More than 1 address would be for different purposes, and thus should be entered as a different entry,.</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.address</t>
+  </si>
+  <si>
+    <t>Organization.contact:officialContact.organization</t>
+  </si>
+  <si>
+    <t>Organization.contact.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|5.0.0)
+</t>
+  </si>
+  <si>
+    <t>This contact detail is handled/monitored by a specific organization</t>
+  </si>
+  <si>
+    <t>This contact detail is handled/monitored by a specific organization. If the name is provided in the contact, then it is referring to the named individual within this organization.</t>
+  </si>
+  <si>
+    <t>Some specific types of contact information can be an handled by an organization (eg legal council is via a specific firm).</t>
+  </si>
+  <si>
+    <t>ExtendedContactDetail.organization</t>
+  </si>
+  <si>
+    <t>Organization.contact:officialContact.period</t>
+  </si>
+  <si>
+    <t>Organization.contact.period</t>
   </si>
   <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>Time period when name was/is in use</t>
-  </si>
-  <si>
-    <t>Indicates the period of time when this name was valid for the named person.</t>
-  </si>
-  <si>
-    <t>Allows names to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>HumanName.period</t>
-  </si>
-  <si>
-    <t>XPN.13 + XPN.14</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.telecom</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>Contact details (e.g.phone/fax/url)</t>
-  </si>
-  <si>
-    <t>The contact details application for the purpose defined.</t>
-  </si>
-  <si>
-    <t>ExtendedContactDetail.telecom</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.address</t>
-  </si>
-  <si>
-    <t>Organization.contact.address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address
-</t>
-  </si>
-  <si>
-    <t>Address for the contact</t>
-  </si>
-  <si>
-    <t>Address for the contact.</t>
-  </si>
-  <si>
-    <t>More than 1 address would be for different purposes, and thus should be entered as a different entry,.</t>
-  </si>
-  <si>
-    <t>ExtendedContactDetail.address</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.organization</t>
-  </si>
-  <si>
-    <t>Organization.contact.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|5.0.0)
-</t>
-  </si>
-  <si>
-    <t>This contact detail is handled/monitored by a specific organization</t>
-  </si>
-  <si>
-    <t>This contact detail is handled/monitored by a specific organization. If the name is provided in the contact, then it is referring to the named individual within this organization.</t>
-  </si>
-  <si>
-    <t>Some specific types of contact information can be an handled by an organization (eg legal council is via a specific firm).</t>
-  </si>
-  <si>
-    <t>ExtendedContactDetail.organization</t>
-  </si>
-  <si>
-    <t>Organization.contact:dpo.period</t>
-  </si>
-  <si>
-    <t>Organization.contact.period</t>
-  </si>
-  <si>
     <t>Period that this contact was valid for usage</t>
   </si>
   <si>
@@ -1082,60 +876,76 @@
     <t>ExtendedContactDetail.period</t>
   </si>
   <si>
-    <t>Organization.contact:incident</t>
-  </si>
-  <si>
-    <t>incident</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.id</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.purpose</t>
+    <t>Organization.contact:dpo</t>
+  </si>
+  <si>
+    <t>dpo</t>
+  </si>
+  <si>
+    <t>Data Protection Officer</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.id</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.purpose</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/contactentity-type"/&gt;
-    &lt;code value="PATINF"/&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-contact-purpose-cs"/&gt;
+    &lt;code value="dpo"/&gt;
+    &lt;display value="Data Protection Officer"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Organization.contact:dpo.name</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.telecom</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.address</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.organization</t>
+  </si>
+  <si>
+    <t>Organization.contact:dpo.period</t>
+  </si>
+  <si>
+    <t>Organization.contact:incident</t>
+  </si>
+  <si>
+    <t>incident</t>
+  </si>
+  <si>
+    <t>AI Incident Reporting Contact</t>
+  </si>
+  <si>
+    <t>Organization.contact:incident.id</t>
+  </si>
+  <si>
+    <t>Organization.contact:incident.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact:incident.purpose</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://example.org/fhir/eu-ai-transparency/CodeSystem/eu-ai-contact-purpose-cs"/&gt;
+    &lt;code value="ai-incident-reporting"/&gt;
+    &lt;display value="AI Incident Reporting Contact"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Organization.contact:incident.name</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.id</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.use</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.text</t>
-  </si>
-  <si>
-    <t>AI Incident Reporting Contact</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.family</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.given</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.prefix</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.suffix</t>
-  </si>
-  <si>
-    <t>Organization.contact:incident.name.period</t>
   </si>
   <si>
     <t>Organization.contact:incident.telecom</t>
@@ -1573,12 +1383,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO63"/>
+  <dimension ref="A1:AO54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.33984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.50390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.21484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1612,7 +1422,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="48.16015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="26.69140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="58.90234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="25.11328125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="187.0625" customWidth="true" bestFit="true"/>
@@ -3151,7 +2961,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>182</v>
       </c>
@@ -3164,13 +2974,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -3519,7 +3329,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>77</v>
@@ -3638,7 +3448,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>87</v>
@@ -3656,7 +3466,7 @@
         <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>206</v>
@@ -3746,10 +3556,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3775,10 +3585,10 @@
         <v>89</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3829,7 +3639,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3838,7 +3648,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>18</v>
@@ -3861,10 +3671,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3893,7 +3703,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>138</v>
@@ -3934,10 +3744,10 @@
         <v>18</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>18</v>
@@ -3946,7 +3756,7 @@
         <v>210</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3978,10 +3788,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4007,13 +3817,13 @@
         <v>170</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4024,7 +3834,7 @@
         <v>18</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>18</v>
@@ -4039,13 +3849,13 @@
         <v>18</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>18</v>
@@ -4063,7 +3873,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4095,10 +3905,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4121,16 +3931,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4180,7 +3990,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4210,12 +4020,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4223,28 +4033,28 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4295,19 +4105,19 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
@@ -4316,7 +4126,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>18</v>
@@ -4327,21 +4137,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
@@ -4350,19 +4160,19 @@
         <v>18</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4400,31 +4210,31 @@
         <v>18</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
@@ -4433,7 +4243,7 @@
         <v>18</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>18</v>
@@ -4444,10 +4254,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4464,25 +4274,23 @@
         <v>18</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -4507,13 +4315,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>254</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -4531,7 +4339,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4549,24 +4357,24 @@
         <v>18</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>257</v>
+        <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4589,20 +4397,18 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>183</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4650,7 +4456,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4668,10 +4474,10 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>18</v>
@@ -4680,16 +4486,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>271</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4699,27 +4507,29 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
       </c>
@@ -4767,53 +4577,53 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>211</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>212</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4822,20 +4632,18 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>18</v>
@@ -4884,46 +4692,46 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>288</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4939,18 +4747,20 @@
         <v>18</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>136</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -4987,19 +4797,19 @@
         <v>18</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5011,30 +4821,30 @@
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>294</v>
+        <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5042,10 +4852,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5057,15 +4867,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5075,7 +4887,7 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>18</v>
+        <v>278</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>18</v>
@@ -5090,13 +4902,13 @@
         <v>18</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>18</v>
+        <v>235</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>18</v>
@@ -5114,13 +4926,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -5132,10 +4944,10 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>302</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5144,12 +4956,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5163,7 +4975,7 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -5172,18 +4984,18 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>240</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5231,13 +5043,13 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
@@ -5249,24 +5061,24 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>313</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5289,13 +5101,13 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>247</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5346,7 +5158,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5378,10 +5190,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5404,16 +5216,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5463,7 +5275,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>257</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5495,10 +5307,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>259</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5521,17 +5333,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>261</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>262</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>263</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -5580,7 +5392,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5612,10 +5424,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>266</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5638,16 +5450,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>338</v>
+        <v>270</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5697,7 +5509,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>271</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5729,13 +5541,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>18</v>
@@ -5760,7 +5572,7 @@
         <v>204</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>206</v>
@@ -5850,10 +5662,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5879,10 +5691,10 @@
         <v>89</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5933,7 +5745,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5942,7 +5754,7 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>18</v>
@@ -5965,10 +5777,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5997,7 +5809,7 @@
         <v>136</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>138</v>
@@ -6038,10 +5850,10 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>18</v>
@@ -6050,7 +5862,7 @@
         <v>210</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6082,10 +5894,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6111,13 +5923,13 @@
         <v>170</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6128,7 +5940,7 @@
         <v>18</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>345</v>
+        <v>290</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>18</v>
@@ -6143,13 +5955,13 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
@@ -6167,7 +5979,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6197,12 +6009,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6213,10 +6025,10 @@
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -6225,16 +6037,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6284,7 +6096,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6314,12 +6126,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6327,28 +6139,28 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>89</v>
+        <v>247</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6399,19 +6211,19 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
@@ -6420,7 +6232,7 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6431,21 +6243,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
@@ -6454,19 +6266,19 @@
         <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6504,31 +6316,31 @@
         <v>18</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>224</v>
+        <v>18</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
@@ -6537,7 +6349,7 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>18</v>
@@ -6548,10 +6360,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6568,25 +6380,23 @@
         <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>18</v>
@@ -6611,13 +6421,13 @@
         <v>18</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>254</v>
+        <v>18</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>18</v>
@@ -6635,7 +6445,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6653,24 +6463,24 @@
         <v>18</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>257</v>
+        <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>258</v>
+        <v>18</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>259</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6693,20 +6503,18 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>267</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
       </c>
@@ -6754,7 +6562,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6772,10 +6580,10 @@
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>268</v>
+        <v>18</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6786,14 +6594,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>271</v>
+        <v>18</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6812,18 +6620,18 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -6871,7 +6679,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6889,28 +6697,28 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>278</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6926,21 +6734,21 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>302</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
       </c>
@@ -6988,7 +6796,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7006,24 +6814,24 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>288</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7043,16 +6851,16 @@
         <v>18</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>307</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7103,7 +6911,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7121,24 +6929,24 @@
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>295</v>
+        <v>181</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>296</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7149,7 +6957,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7158,16 +6966,16 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>299</v>
+        <v>218</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7218,28 +7026,28 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>301</v>
+        <v>220</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>18</v>
+        <v>221</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>302</v>
+        <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7250,21 +7058,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
@@ -7273,21 +7081,21 @@
         <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>306</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>307</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7335,74 +7143,78 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
         <v>313</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>18</v>
+        <v>314</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7450,7 +7262,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7462,7 +7274,7 @@
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
@@ -7471,7 +7283,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7482,10 +7294,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7496,7 +7308,7 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>18</v>
@@ -7505,21 +7317,21 @@
         <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>322</v>
+        <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
       </c>
@@ -7567,13 +7379,13 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
@@ -7588,7 +7400,7 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>18</v>
@@ -7599,10 +7411,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7610,7 +7422,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
@@ -7622,21 +7434,19 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>329</v>
+        <v>170</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>332</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -7660,10 +7470,10 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>18</v>
@@ -7684,10 +7494,10 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>87</v>
@@ -7705,7 +7515,7 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>18</v>
@@ -7716,10 +7526,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7739,21 +7549,21 @@
         <v>18</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -7801,7 +7611,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7822,7 +7632,7 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>18</v>
@@ -7833,10 +7643,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7856,21 +7666,19 @@
         <v>18</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -7918,7 +7726,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7936,1067 +7744,20 @@
         <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>365</v>
+        <v>181</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO63" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO63">
+  <autoFilter ref="A1:AO54">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9006,7 +7767,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI53">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="339">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,38 +433,61 @@
     <t>Organization.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Organization.extension:DPIAReference</t>
+  </si>
+  <si>
+    <t>DPIAReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/fhir/eu-ai-transparency/StructureDefinition/eu-ai-dpia-reference}
+</t>
+  </si>
+  <si>
+    <t>Reference to the DPIA Document</t>
+  </si>
+  <si>
+    <t>Privacy risk management, GDPR accountability</t>
+  </si>
+  <si>
+    <t>Organization.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Organization.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
@@ -677,9 +700,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 org-3:The telecom of an organization can never be of use 'home' {telecom.where(use = 'home').empty()}org-4:The address of an organization can never be of use 'home' {address.where(use = 'home').empty()}</t>
   </si>
@@ -721,11 +741,10 @@
     <t>Organization.contact.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -1383,12 +1402,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.50390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.21484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.61328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1396,7 +1415,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="76.46875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2377,7 +2396,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2396,17 +2415,15 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>18</v>
@@ -2443,16 +2460,14 @@
         <v>18</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2476,7 +2491,7 @@
         <v>18</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>18</v>
@@ -2485,48 +2500,46 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>18</v>
       </c>
@@ -2574,7 +2587,7 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2595,7 +2608,7 @@
         <v>18</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>18</v>
@@ -2613,7 +2626,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2626,13 +2639,13 @@
         <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>148</v>
@@ -2640,9 +2653,11 @@
       <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>18</v>
@@ -2691,7 +2706,7 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2700,33 +2715,33 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>156</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2737,117 +2752,113 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2858,36 +2869,38 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
         <v>18</v>
       </c>
@@ -2907,13 +2920,13 @@
         <v>18</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>176</v>
+        <v>18</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -2931,13 +2944,13 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>18</v>
@@ -2946,27 +2959,27 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2974,13 +2987,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -2989,19 +3002,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>18</v>
@@ -3026,13 +3039,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -3050,42 +3063,42 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3093,34 +3106,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
@@ -3169,16 +3182,16 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
@@ -3187,24 +3200,24 @@
         <v>18</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>18</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3215,7 +3228,7 @@
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
@@ -3224,20 +3237,22 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3286,13 +3301,13 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
@@ -3307,7 +3322,7 @@
         <v>18</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>18</v>
@@ -3318,10 +3333,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3329,11 +3344,11 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3341,20 +3356,18 @@
         <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
         <v>207</v>
       </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
         <v>208</v>
       </c>
@@ -3393,56 +3406,56 @@
         <v>18</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AC17" s="2"/>
-      <c r="AD17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AF17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>18</v>
       </c>
@@ -3451,10 +3464,10 @@
         <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -3463,19 +3476,19 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -3512,19 +3525,17 @@
         <v>18</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3536,7 +3547,7 @@
         <v>18</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>18</v>
@@ -3545,7 +3556,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>18</v>
@@ -3554,26 +3565,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -3582,16 +3595,20 @@
         <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
@@ -3639,19 +3656,19 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>18</v>
@@ -3660,7 +3677,7 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>18</v>
@@ -3678,14 +3695,14 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -3697,17 +3714,15 @@
         <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -3744,31 +3759,31 @@
         <v>18</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AC20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AG20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ20" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>18</v>
@@ -3777,7 +3792,7 @@
         <v>18</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>18</v>
@@ -3795,14 +3810,14 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -3811,10 +3826,10 @@
         <v>18</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>230</v>
@@ -3823,7 +3838,7 @@
         <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3834,58 +3849,58 @@
         <v>18</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="T21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>18</v>
@@ -3894,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
@@ -3905,10 +3920,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3916,10 +3931,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -3931,16 +3946,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3951,7 +3966,7 @@
         <v>18</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>18</v>
@@ -3966,13 +3981,13 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -3990,13 +4005,13 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
@@ -4020,12 +4035,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4033,13 +4048,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -4048,15 +4063,17 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4135,7 +4152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>251</v>
       </c>
@@ -4148,13 +4165,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -4171,9 +4188,7 @@
       <c r="M24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4222,13 +4237,13 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>18</v>
@@ -4254,10 +4269,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4280,18 +4295,18 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4339,7 +4354,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4371,10 +4386,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4397,18 +4412,18 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>18</v>
       </c>
@@ -4456,7 +4471,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4486,16 +4501,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>273</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>18</v>
       </c>
@@ -4507,29 +4520,27 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>18</v>
       </c>
@@ -4577,19 +4588,19 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
@@ -4598,7 +4609,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4607,14 +4618,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>18</v>
       </c>
@@ -4626,7 +4639,7 @@
         <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -4635,16 +4648,20 @@
         <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>18</v>
       </c>
@@ -4692,19 +4709,19 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>18</v>
@@ -4713,7 +4730,7 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>18</v>
@@ -4724,21 +4741,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -4750,17 +4767,15 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -4797,31 +4812,31 @@
         <v>18</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>18</v>
@@ -4830,7 +4845,7 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -4841,21 +4856,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>229</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -4864,10 +4879,10 @@
         <v>18</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>230</v>
@@ -4876,7 +4891,7 @@
         <v>231</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4887,7 +4902,7 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>18</v>
@@ -4902,66 +4917,66 @@
         <v>18</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4969,13 +4984,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -4984,16 +4999,16 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5004,7 +5019,7 @@
         <v>18</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>18</v>
+        <v>284</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>18</v>
@@ -5019,13 +5034,13 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>18</v>
@@ -5043,13 +5058,13 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
@@ -5075,10 +5090,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5086,10 +5101,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>88</v>
@@ -5101,15 +5116,17 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5188,9 +5205,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>252</v>
@@ -5201,13 +5218,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -5224,9 +5241,7 @@
       <c r="M33" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5275,13 +5290,13 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>18</v>
@@ -5307,10 +5322,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5333,18 +5348,18 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
       </c>
@@ -5392,7 +5407,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5424,10 +5439,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5450,18 +5465,18 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -5509,7 +5524,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5539,16 +5554,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>18</v>
       </c>
@@ -5560,29 +5573,27 @@
         <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -5630,19 +5641,19 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
@@ -5651,7 +5662,7 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>18</v>
@@ -5660,14 +5671,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>18</v>
       </c>
@@ -5679,7 +5692,7 @@
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>18</v>
@@ -5688,16 +5701,20 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>89</v>
+        <v>211</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
       </c>
@@ -5745,19 +5762,19 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
@@ -5766,7 +5783,7 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -5777,21 +5794,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>223</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -5803,17 +5820,15 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -5850,31 +5865,31 @@
         <v>18</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="AC38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AF38" t="s" s="2">
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI38" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -5883,7 +5898,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -5894,21 +5909,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>229</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
@@ -5917,10 +5932,10 @@
         <v>18</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>230</v>
@@ -5929,7 +5944,7 @@
         <v>231</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5940,7 +5955,7 @@
         <v>18</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>290</v>
+        <v>18</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>18</v>
@@ -5955,66 +5970,66 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6022,13 +6037,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -6037,16 +6052,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6057,7 +6072,7 @@
         <v>18</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>18</v>
@@ -6072,13 +6087,13 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6096,13 +6111,13 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
@@ -6128,10 +6143,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6139,10 +6154,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>88</v>
@@ -6154,15 +6169,17 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
@@ -6241,9 +6258,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>252</v>
@@ -6254,13 +6271,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -6277,9 +6294,7 @@
       <c r="M42" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>18</v>
@@ -6328,13 +6343,13 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
@@ -6360,10 +6375,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6386,18 +6401,18 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -6445,7 +6460,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6477,10 +6492,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6503,18 +6518,18 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>18</v>
       </c>
@@ -6562,7 +6577,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6594,10 +6609,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6620,18 +6635,18 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>18</v>
       </c>
@@ -6679,7 +6694,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6697,24 +6712,24 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>300</v>
+        <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6725,7 +6740,7 @@
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -6734,10 +6749,10 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>303</v>
@@ -6796,13 +6811,13 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
@@ -6814,24 +6829,24 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>18</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6854,16 +6869,18 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -6911,7 +6928,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6929,10 +6946,10 @@
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -6943,10 +6960,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6957,7 +6974,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -6969,13 +6986,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>313</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>218</v>
+        <v>314</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>219</v>
+        <v>315</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7026,28 +7043,28 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>18</v>
+        <v>316</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>18</v>
@@ -7058,21 +7075,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
@@ -7084,17 +7101,15 @@
         <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -7143,19 +7158,19 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI49" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
@@ -7164,7 +7179,7 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7175,14 +7190,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>314</v>
+        <v>147</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7195,26 +7210,24 @@
         <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>315</v>
+        <v>230</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>316</v>
+        <v>231</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
       </c>
@@ -7262,7 +7275,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>317</v>
+        <v>233</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7283,7 +7296,7 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7294,14 +7307,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7314,23 +7327,25 @@
         <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>321</v>
+        <v>151</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7379,7 +7394,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7391,7 +7406,7 @@
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
@@ -7400,7 +7415,7 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>18</v>
@@ -7411,10 +7426,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7422,10 +7437,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -7437,16 +7452,18 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -7470,10 +7487,10 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>18</v>
@@ -7494,13 +7511,13 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>18</v>
@@ -7515,7 +7532,7 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>18</v>
@@ -7526,10 +7543,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7537,7 +7554,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>87</v>
@@ -7552,18 +7569,16 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>18</v>
       </c>
@@ -7587,10 +7602,10 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>18</v>
+        <v>331</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>18</v>
@@ -7611,10 +7626,10 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>87</v>
@@ -7632,7 +7647,7 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>18</v>
@@ -7643,10 +7658,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7669,16 +7684,18 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
       </c>
@@ -7726,7 +7743,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7747,17 +7764,132 @@
         <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO54">
+  <autoFilter ref="A1:AO55">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7767,7 +7899,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI54">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
